--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484643_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484643_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2341</v>
+        <v>4.0532</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4569</v>
+        <v>4.1273</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2228</v>
+        <v>-0.0742</v>
       </c>
       <c r="G2" t="n">
         <v>2.344</v>
@@ -610,13 +610,13 @@
         <v>0.733</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8389</v>
+        <v>1.658</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9322</v>
+        <v>0.6026</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.0554</v>
       </c>
       <c r="V2" t="n">
         <v>1.1507</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0247</v>
+        <v>2.1675</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2442</v>
+        <v>2.4365</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2195</v>
+        <v>-0.269</v>
       </c>
       <c r="G3" t="n">
         <v>2.2221</v>
@@ -688,13 +688,13 @@
         <v>0.733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0142</v>
+        <v>0.1286</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3303</v>
+        <v>-0.138</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3161</v>
+        <v>0.2666</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0164</v>
+        <v>0.6211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5737</v>
+        <v>1.5397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4427</v>
+        <v>-0.9186</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.9722</v>
+        <v>-1.6449</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2122</v>
+        <v>-1.2119</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.76</v>
+        <v>-0.433</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2808</v>
+        <v>1.9473</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3225</v>
+        <v>1.7707</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0417</v>
+        <v>0.1765</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6914</v>
+        <v>-3.5922</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8898</v>
+        <v>-2.9827</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8017</v>
+        <v>-0.6095</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0158</v>
+        <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5971</v>
+        <v>1.3377</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6637</v>
+        <v>-0.164</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9335</v>
+        <v>1.5016</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0407</v>
+        <v>0.1953</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8559</v>
+        <v>1.5889</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1848</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>N. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6055</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0038</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3983</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6449</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2119</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.433</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9473</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7707</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5922</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9827</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6095</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3221</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6998</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.0219</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. RAMON AÑIBARRO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>-0.2806</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>-0.5251</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.2445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>-2.9722</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-2.2122</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>-0.2808</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>-0.3225</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.6914</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.8898</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3002</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.5649</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.7353</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.0407</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1848</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4542</v>
+        <v>-0.3799</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9163</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4621</v>
+        <v>0.5364</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7784</v>
@@ -1000,13 +1000,13 @@
         <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4821</v>
+        <v>-0.4078</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V7" t="n">
         <v>0.6231</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. BOYENZA</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4244</v>
+        <v>-1.1963</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0684</v>
+        <v>-1.8677</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.356</v>
+        <v>0.6714</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1354</v>
+        <v>-1.4939</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4335</v>
+        <v>-3.0358</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2981</v>
+        <v>1.5419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0417</v>
+        <v>-0.497</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.8147</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0417</v>
+        <v>1.3177</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1771</v>
+        <v>-0.9968</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4335</v>
+        <v>-1.2211</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2564</v>
+        <v>0.2243</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2053</v>
+        <v>-0.3805</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1101</v>
+        <v>-0.4544</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>S. BOYENZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4906</v>
+        <v>-1.3748</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9639</v>
+        <v>-0.0684</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4732</v>
+        <v>-1.3064</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4939</v>
+        <v>-0.1354</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0358</v>
+        <v>-0.4335</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5419</v>
+        <v>0.2981</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.497</v>
+        <v>0.0417</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3177</v>
+        <v>0.0417</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9968</v>
+        <v>-0.1771</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2211</v>
+        <v>-0.4335</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2243</v>
+        <v>0.2564</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6748</v>
+        <v>-0.1557</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5505</v>
+        <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1243</v>
+        <v>-0.0456</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3115</v>
+        <v>-1.267</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3115</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5489</v>
+        <v>-2.0189</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.55</v>
+        <v>-1.8219</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0011</v>
+        <v>-0.197</v>
       </c>
       <c r="G10" t="n">
         <v>-6.7855</v>
@@ -1234,13 +1234,13 @@
         <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1801</v>
+        <v>0.71</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2307</v>
+        <v>-0.5026</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4108</v>
+        <v>1.2126</v>
       </c>
       <c r="V10" t="n">
         <v>2.4072</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3375</v>
+        <v>-3.9526</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8412</v>
+        <v>-4.5554</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5037</v>
+        <v>0.6028</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0856</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2192</v>
+        <v>0.6041</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6569</v>
+        <v>-0.0573</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5623</v>
+        <v>0.6614</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0208</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0924</v>
+        <v>-4.8306</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1719</v>
+        <v>-2.3065</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9205</v>
+        <v>-2.5241</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9148</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0118</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3499</v>
+        <v>0.5155</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3381</v>
+        <v>0.7345</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3491</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1422</v>
+        <v>-6.866799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.907999999999999</v>
+        <v>-3.632699999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2343</v>
+        <v>-3.2342</v>
       </c>
       <c r="G13" t="n">
         <v>-17.9195</v>
@@ -1441,13 +1441,13 @@
         <v>-2.8854</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04160000000000164</v>
+        <v>0.04159999999999986</v>
       </c>
       <c r="K13" t="n">
         <v>-0.1208000000000009</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1621999999999997</v>
+        <v>0.1622000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-17.9609</v>
@@ -1459,7 +1459,7 @@
         <v>-3.0475</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9163999999999998</v>
+        <v>0.9164</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.9118</v>
@@ -1468,13 +1468,13 @@
         <v>12.828</v>
       </c>
       <c r="S13" t="n">
-        <v>5.769200000000001</v>
+        <v>6.0446</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2937999999999997</v>
+        <v>-0.01870000000000016</v>
       </c>
       <c r="U13" t="n">
-        <v>6.063099999999999</v>
+        <v>6.063199999999999</v>
       </c>
       <c r="V13" t="n">
         <v>4.091600000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4418</v>
+        <v>5.7629</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4099</v>
+        <v>4.9291</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0319</v>
+        <v>0.8337</v>
       </c>
       <c r="G14" t="n">
         <v>5.335</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7849</v>
+        <v>0.106</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1441</v>
+        <v>-0.3367</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6408</v>
+        <v>0.4427</v>
       </c>
       <c r="V14" t="n">
         <v>0.3219</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5317</v>
+        <v>3.5594</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5495</v>
+        <v>3.4533</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0178</v>
+        <v>0.106</v>
       </c>
       <c r="G15" t="n">
         <v>4.7816</v>
@@ -1624,13 +1624,13 @@
         <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1557</v>
+        <v>0.1834</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1116</v>
+        <v>-0.2077</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2673</v>
+        <v>0.3912</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5889</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0019</v>
+        <v>2.2219</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6083</v>
+        <v>2.7045</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.4826</v>
       </c>
       <c r="G16" t="n">
         <v>3.1577</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3103</v>
+        <v>-1.0903</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8258</v>
+        <v>-0.7296</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4846</v>
+        <v>-0.3607</v>
       </c>
       <c r="V16" t="n">
         <v>-0.945</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3252</v>
+        <v>0.5255</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0761</v>
+        <v>0.128</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7509</v>
+        <v>0.3976</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7055</v>
+        <v>1.53</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6862</v>
+        <v>1.3757</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0193</v>
+        <v>0.1543</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3423</v>
+        <v>2.031</v>
       </c>
       <c r="K20" t="n">
-        <v>0.842</v>
+        <v>1.2354</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5003</v>
+        <v>0.7956</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6368</v>
+        <v>-0.5011</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1558</v>
+        <v>0.1403</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.481</v>
+        <v>-0.6413</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4798</v>
+        <v>-1.4155</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3499</v>
+        <v>-0.9868</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1299</v>
+        <v>-0.4288</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2807</v>
+        <v>-0.2576</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0318</v>
+        <v>0.6915</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2489</v>
+        <v>-0.949</v>
       </c>
       <c r="G21" t="n">
-        <v>1.53</v>
+        <v>1.7055</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3757</v>
+        <v>0.6862</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1543</v>
+        <v>1.0193</v>
       </c>
       <c r="J21" t="n">
-        <v>2.031</v>
+        <v>2.3423</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2354</v>
+        <v>0.842</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7956</v>
+        <v>1.5003</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5011</v>
+        <v>-0.6368</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1403</v>
+        <v>-0.1558</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6413</v>
+        <v>-0.481</v>
       </c>
       <c r="P21" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6603</v>
+        <v>-1.0626</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0829</v>
+        <v>-0.7345</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5774</v>
+        <v>-0.3281</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9769</v>
+        <v>-0.4436</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6479</v>
+        <v>-1.2632</v>
       </c>
       <c r="F22" t="n">
-        <v>0.671</v>
+        <v>0.8196</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6183</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0367</v>
+        <v>-0.5034</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2111</v>
+        <v>-0.8265</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1745</v>
+        <v>0.3231</v>
       </c>
       <c r="V22" t="n">
         <v>0.3115</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4549</v>
+        <v>-1.7471</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8913</v>
+        <v>-1.5324</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4364</v>
+        <v>-0.2147</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9046</v>
+        <v>-1.5501</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.3122</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8337</v>
+        <v>-1.8623</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.472</v>
+        <v>-1.092</v>
       </c>
       <c r="K23" t="n">
-        <v>0.201</v>
+        <v>0.065</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.673</v>
+        <v>-1.157</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4326</v>
+        <v>-0.4581</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2719</v>
+        <v>0.2472</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1606</v>
+        <v>-0.7053</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.099</v>
+        <v>-0.7468</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9374</v>
+        <v>-0.4404</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0364</v>
+        <v>-0.3064</v>
       </c>
       <c r="V23" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.871</v>
+        <v>-2.0247</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5324</v>
+        <v>-3.8913</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3385</v>
+        <v>1.8666</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5501</v>
+        <v>-1.9046</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3122</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8623</v>
+        <v>-1.8337</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.092</v>
+        <v>-1.472</v>
       </c>
       <c r="K24" t="n">
-        <v>0.065</v>
+        <v>0.201</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.157</v>
+        <v>-1.673</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4581</v>
+        <v>-0.4326</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2472</v>
+        <v>-0.2719</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7053</v>
+        <v>-0.1606</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5498</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8707</v>
+        <v>-0.4708</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4404</v>
+        <v>-0.9374</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4302</v>
+        <v>0.4666</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.1063</v>
+        <v>-2.0568</v>
       </c>
       <c r="E25" t="n">
         <v>-1.3839</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7225</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9011</v>
@@ -2404,13 +2404,13 @@
         <v>0.1833</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3885</v>
+        <v>-0.339</v>
       </c>
       <c r="T25" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2234</v>
+        <v>-0.1738</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1315</v>
+        <v>-3.4991</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.0874</v>
+        <v>-5.7028</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9559</v>
+        <v>2.2037</v>
       </c>
       <c r="G26" t="n">
         <v>2.2823</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0626</v>
+        <v>-0.4302</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0829</v>
+        <v>-0.6983</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0203</v>
+        <v>0.2681</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8692</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>7.142099999999998</v>
+        <v>7.142200000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>3.234100000000001</v>
+        <v>3.234199999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>3.907999999999999</v>
+        <v>3.908</v>
       </c>
       <c r="G27" t="n">
         <v>17.9194</v>
@@ -2545,7 +2545,7 @@
         <v>-0.0415000000000002</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1208000000000001</v>
+        <v>0.1208</v>
       </c>
       <c r="O27" t="n">
         <v>-0.162</v>
@@ -2560,13 +2560,13 @@
         <v>11.9117</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.769299999999999</v>
+        <v>-5.769200000000001</v>
       </c>
       <c r="T27" t="n">
         <v>-6.0631</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2938</v>
+        <v>0.2938999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-4.0916</v>
